--- a/fishershub-tms-ebm-migration-progress.xlsx
+++ b/fishershub-tms-ebm-migration-progress.xlsx
@@ -2996,7 +2996,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" hidden="1">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" hidden="1">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" hidden="1">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" hidden="1">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" hidden="1">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" hidden="1">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" hidden="1">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" hidden="1">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" hidden="1">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" hidden="1">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" hidden="1">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" hidden="1">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" hidden="1">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" hidden="1">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" hidden="1">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" hidden="1">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" hidden="1">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" hidden="1">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" hidden="1">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" hidden="1">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" hidden="1">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" hidden="1">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" hidden="1">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" hidden="1">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" hidden="1">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" hidden="1">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" hidden="1">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" hidden="1">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" hidden="1">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -4226,7 +4226,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" hidden="1">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" hidden="1">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" hidden="1">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -4352,7 +4352,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" hidden="1">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" hidden="1">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" hidden="1">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" hidden="1">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" hidden="1">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" hidden="1">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" hidden="1">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" hidden="1">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" hidden="1">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -4733,7 +4733,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" hidden="1">
       <c r="A44" t="s">
         <v>41</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" hidden="1">
       <c r="A45" t="s">
         <v>42</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" hidden="1">
       <c r="A46" t="s">
         <v>42</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" hidden="1">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" hidden="1">
       <c r="A48" t="s">
         <v>42</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" hidden="1">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" hidden="1">
       <c r="A50" t="s">
         <v>42</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" hidden="1">
       <c r="A51" t="s">
         <v>43</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" hidden="1">
       <c r="A52" t="s">
         <v>43</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" hidden="1">
       <c r="A53" t="s">
         <v>43</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" hidden="1">
       <c r="A54" t="s">
         <v>43</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" hidden="1">
       <c r="A55" t="s">
         <v>43</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" hidden="1">
       <c r="A56" t="s">
         <v>47</v>
       </c>
@@ -5288,7 +5288,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" hidden="1">
       <c r="A57" t="s">
         <v>47</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" hidden="1">
       <c r="A58" t="s">
         <v>47</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" hidden="1">
       <c r="A59" t="s">
         <v>47</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" hidden="1">
       <c r="A60" t="s">
         <v>47</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" hidden="1">
       <c r="A61" t="s">
         <v>47</v>
       </c>
@@ -5498,7 +5498,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" hidden="1">
       <c r="A62" t="s">
         <v>47</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" hidden="1">
       <c r="A63" t="s">
         <v>53</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" hidden="1">
       <c r="A64" t="s">
         <v>53</v>
       </c>
@@ -5627,7 +5627,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" hidden="1">
       <c r="A65" t="s">
         <v>53</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" hidden="1">
       <c r="A66" t="s">
         <v>53</v>
       </c>
@@ -5711,7 +5711,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" hidden="1">
       <c r="A67" t="s">
         <v>53</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" hidden="1">
       <c r="A68" t="s">
         <v>53</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" hidden="1">
       <c r="A69" t="s">
         <v>53</v>
       </c>
@@ -5837,7 +5837,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" hidden="1">
       <c r="A70" t="s">
         <v>54</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" hidden="1">
       <c r="A71" t="s">
         <v>54</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" hidden="1">
       <c r="A72" t="s">
         <v>54</v>
       </c>
@@ -5966,7 +5966,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" hidden="1">
       <c r="A73" t="s">
         <v>54</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" hidden="1">
       <c r="A74" t="s">
         <v>54</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" hidden="1">
       <c r="A75" t="s">
         <v>54</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" hidden="1">
       <c r="A76" t="s">
         <v>54</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" hidden="1">
       <c r="A77" t="s">
         <v>54</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" hidden="1">
       <c r="A78" t="s">
         <v>54</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" hidden="1">
       <c r="A79" t="s">
         <v>61</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" hidden="1">
       <c r="A80" t="s">
         <v>61</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" hidden="1">
       <c r="A81" t="s">
         <v>61</v>
       </c>
@@ -6347,7 +6347,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" hidden="1">
       <c r="A82" t="s">
         <v>61</v>
       </c>
@@ -6389,7 +6389,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" hidden="1">
       <c r="A83" t="s">
         <v>61</v>
       </c>
@@ -6431,7 +6431,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" hidden="1">
       <c r="A84" t="s">
         <v>61</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" hidden="1">
       <c r="A85" t="s">
         <v>61</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" hidden="1">
       <c r="A86" t="s">
         <v>61</v>
       </c>
@@ -6557,7 +6557,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" hidden="1">
       <c r="A87" t="s">
         <v>65</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" hidden="1">
       <c r="A88" t="s">
         <v>65</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" hidden="1">
       <c r="A89" t="s">
         <v>65</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" hidden="1">
       <c r="A90" t="s">
         <v>65</v>
       </c>
@@ -6728,7 +6728,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" hidden="1">
       <c r="A91" t="s">
         <v>65</v>
       </c>
@@ -6770,7 +6770,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" hidden="1">
       <c r="A92" t="s">
         <v>65</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" hidden="1">
       <c r="A93" t="s">
         <v>65</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" hidden="1">
       <c r="A94" t="s">
         <v>66</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" hidden="1">
       <c r="A95" t="s">
         <v>66</v>
       </c>
@@ -6941,7 +6941,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" hidden="1">
       <c r="A96" t="s">
         <v>66</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" hidden="1">
       <c r="A97" t="s">
         <v>66</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" hidden="1">
       <c r="A98" t="s">
         <v>66</v>
       </c>
@@ -7067,7 +7067,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" hidden="1">
       <c r="A99" t="s">
         <v>66</v>
       </c>
@@ -7109,7 +7109,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" hidden="1">
       <c r="A100" t="s">
         <v>66</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" hidden="1">
       <c r="A101" t="s">
         <v>66</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" hidden="1">
       <c r="A102" t="s">
         <v>69</v>
       </c>
@@ -7238,7 +7238,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" hidden="1">
       <c r="A103" t="s">
         <v>69</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" hidden="1">
       <c r="A104" t="s">
         <v>69</v>
       </c>
@@ -7322,7 +7322,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" hidden="1">
       <c r="A105" t="s">
         <v>69</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" hidden="1">
       <c r="A106" t="s">
         <v>69</v>
       </c>
@@ -7406,7 +7406,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" hidden="1">
       <c r="A107" t="s">
         <v>69</v>
       </c>
@@ -7448,7 +7448,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" hidden="1">
       <c r="A108" t="s">
         <v>69</v>
       </c>
@@ -23612,7 +23612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:14">
+    <row r="567" spans="1:14" hidden="1">
       <c r="A567" t="s">
         <v>270</v>
       </c>
@@ -23657,7 +23657,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="568" spans="1:14">
+    <row r="568" spans="1:14" hidden="1">
       <c r="A568" t="s">
         <v>270</v>
       </c>
@@ -23699,7 +23699,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="569" spans="1:14">
+    <row r="569" spans="1:14" hidden="1">
       <c r="A569" t="s">
         <v>270</v>
       </c>
@@ -23741,7 +23741,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="570" spans="1:14">
+    <row r="570" spans="1:14" hidden="1">
       <c r="A570" t="s">
         <v>270</v>
       </c>
@@ -23783,7 +23783,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="571" spans="1:14">
+    <row r="571" spans="1:14" hidden="1">
       <c r="A571" t="s">
         <v>270</v>
       </c>
@@ -23825,7 +23825,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="572" spans="1:14">
+    <row r="572" spans="1:14" hidden="1">
       <c r="A572" t="s">
         <v>270</v>
       </c>
@@ -23867,7 +23867,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="573" spans="1:14">
+    <row r="573" spans="1:14" hidden="1">
       <c r="A573" t="s">
         <v>270</v>
       </c>
@@ -23909,7 +23909,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="574" spans="1:14">
+    <row r="574" spans="1:14" hidden="1">
       <c r="A574" t="s">
         <v>270</v>
       </c>
@@ -23951,7 +23951,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="575" spans="1:14">
+    <row r="575" spans="1:14" hidden="1">
       <c r="A575" t="s">
         <v>272</v>
       </c>
@@ -23996,7 +23996,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="576" spans="1:14">
+    <row r="576" spans="1:14" hidden="1">
       <c r="A576" t="s">
         <v>272</v>
       </c>
@@ -24038,7 +24038,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="577" spans="1:14">
+    <row r="577" spans="1:14" hidden="1">
       <c r="A577" t="s">
         <v>272</v>
       </c>
@@ -24080,7 +24080,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="578" spans="1:14">
+    <row r="578" spans="1:14" hidden="1">
       <c r="A578" t="s">
         <v>272</v>
       </c>
@@ -24122,7 +24122,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="579" spans="1:14">
+    <row r="579" spans="1:14" hidden="1">
       <c r="A579" t="s">
         <v>272</v>
       </c>
@@ -24164,7 +24164,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="580" spans="1:14">
+    <row r="580" spans="1:14" hidden="1">
       <c r="A580" t="s">
         <v>272</v>
       </c>
@@ -24206,7 +24206,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="581" spans="1:14">
+    <row r="581" spans="1:14" hidden="1">
       <c r="A581" t="s">
         <v>275</v>
       </c>
@@ -24245,7 +24245,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="582" spans="1:14">
+    <row r="582" spans="1:14" hidden="1">
       <c r="A582" t="s">
         <v>275</v>
       </c>
@@ -24281,7 +24281,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="583" spans="1:14">
+    <row r="583" spans="1:14" hidden="1">
       <c r="A583" t="s">
         <v>275</v>
       </c>
@@ -24317,7 +24317,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="584" spans="1:14">
+    <row r="584" spans="1:14" hidden="1">
       <c r="A584" t="s">
         <v>275</v>
       </c>
@@ -24353,7 +24353,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="585" spans="1:14">
+    <row r="585" spans="1:14" hidden="1">
       <c r="A585" t="s">
         <v>275</v>
       </c>
@@ -24389,7 +24389,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="586" spans="1:14">
+    <row r="586" spans="1:14" hidden="1">
       <c r="A586" t="s">
         <v>275</v>
       </c>
@@ -24425,7 +24425,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="587" spans="1:14">
+    <row r="587" spans="1:14" hidden="1">
       <c r="A587" t="s">
         <v>275</v>
       </c>
@@ -24461,7 +24461,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="588" spans="1:14">
+    <row r="588" spans="1:14" hidden="1">
       <c r="A588" t="s">
         <v>275</v>
       </c>
@@ -24497,7 +24497,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="589" spans="1:14">
+    <row r="589" spans="1:14" hidden="1">
       <c r="A589" t="s">
         <v>275</v>
       </c>
@@ -24533,7 +24533,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="590" spans="1:14">
+    <row r="590" spans="1:14" hidden="1">
       <c r="A590" t="s">
         <v>275</v>
       </c>
@@ -24569,7 +24569,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="591" spans="1:14">
+    <row r="591" spans="1:14" hidden="1">
       <c r="A591" t="s">
         <v>275</v>
       </c>
@@ -24605,7 +24605,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="592" spans="1:14">
+    <row r="592" spans="1:14" hidden="1">
       <c r="A592" t="s">
         <v>275</v>
       </c>
@@ -24641,7 +24641,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="593" spans="1:14">
+    <row r="593" spans="1:14" hidden="1">
       <c r="A593" t="s">
         <v>275</v>
       </c>
@@ -24677,7 +24677,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="594" spans="1:14">
+    <row r="594" spans="1:14" hidden="1">
       <c r="A594" t="s">
         <v>283</v>
       </c>
@@ -24722,7 +24722,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="595" spans="1:14">
+    <row r="595" spans="1:14" hidden="1">
       <c r="A595" t="s">
         <v>283</v>
       </c>
@@ -24764,7 +24764,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="596" spans="1:14">
+    <row r="596" spans="1:14" hidden="1">
       <c r="A596" t="s">
         <v>283</v>
       </c>
@@ -24806,7 +24806,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="597" spans="1:14">
+    <row r="597" spans="1:14" hidden="1">
       <c r="A597" t="s">
         <v>283</v>
       </c>
@@ -24848,7 +24848,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="598" spans="1:14">
+    <row r="598" spans="1:14" hidden="1">
       <c r="A598" t="s">
         <v>283</v>
       </c>
@@ -24890,7 +24890,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="599" spans="1:14">
+    <row r="599" spans="1:14" hidden="1">
       <c r="A599" t="s">
         <v>284</v>
       </c>
@@ -24935,7 +24935,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="600" spans="1:14">
+    <row r="600" spans="1:14" hidden="1">
       <c r="A600" t="s">
         <v>284</v>
       </c>
@@ -24977,7 +24977,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="601" spans="1:14">
+    <row r="601" spans="1:14" hidden="1">
       <c r="A601" t="s">
         <v>284</v>
       </c>
@@ -25019,7 +25019,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="602" spans="1:14">
+    <row r="602" spans="1:14" hidden="1">
       <c r="A602" t="s">
         <v>284</v>
       </c>
@@ -25061,7 +25061,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="603" spans="1:14">
+    <row r="603" spans="1:14" hidden="1">
       <c r="A603" t="s">
         <v>284</v>
       </c>
@@ -25103,7 +25103,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="604" spans="1:14">
+    <row r="604" spans="1:14" hidden="1">
       <c r="A604" t="s">
         <v>284</v>
       </c>
@@ -25145,7 +25145,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="605" spans="1:14">
+    <row r="605" spans="1:14" hidden="1">
       <c r="A605" t="s">
         <v>284</v>
       </c>
@@ -25187,7 +25187,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="606" spans="1:14">
+    <row r="606" spans="1:14" hidden="1">
       <c r="A606" t="s">
         <v>284</v>
       </c>
@@ -25229,7 +25229,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="607" spans="1:14">
+    <row r="607" spans="1:14" hidden="1">
       <c r="A607" t="s">
         <v>284</v>
       </c>
@@ -25271,7 +25271,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="608" spans="1:14">
+    <row r="608" spans="1:14" hidden="1">
       <c r="A608" t="s">
         <v>284</v>
       </c>
@@ -25313,7 +25313,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="609" spans="1:14">
+    <row r="609" spans="1:14" hidden="1">
       <c r="A609" t="s">
         <v>284</v>
       </c>
@@ -25355,7 +25355,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="610" spans="1:14">
+    <row r="610" spans="1:14" hidden="1">
       <c r="A610" t="s">
         <v>284</v>
       </c>
@@ -25397,7 +25397,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="611" spans="1:14">
+    <row r="611" spans="1:14" hidden="1">
       <c r="A611" t="s">
         <v>284</v>
       </c>
@@ -25439,7 +25439,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="612" spans="1:14">
+    <row r="612" spans="1:14" hidden="1">
       <c r="A612" t="s">
         <v>284</v>
       </c>
@@ -25481,7 +25481,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="613" spans="1:14">
+    <row r="613" spans="1:14" hidden="1">
       <c r="A613" t="s">
         <v>284</v>
       </c>
@@ -25523,7 +25523,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="614" spans="1:14">
+    <row r="614" spans="1:14" hidden="1">
       <c r="A614" t="s">
         <v>292</v>
       </c>
@@ -25568,7 +25568,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="615" spans="1:14">
+    <row r="615" spans="1:14" hidden="1">
       <c r="A615" t="s">
         <v>292</v>
       </c>
@@ -25610,7 +25610,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="616" spans="1:14">
+    <row r="616" spans="1:14" hidden="1">
       <c r="A616" t="s">
         <v>292</v>
       </c>
@@ -25652,7 +25652,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="617" spans="1:14">
+    <row r="617" spans="1:14" hidden="1">
       <c r="A617" t="s">
         <v>292</v>
       </c>
@@ -25694,7 +25694,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="618" spans="1:14">
+    <row r="618" spans="1:14" hidden="1">
       <c r="A618" t="s">
         <v>292</v>
       </c>
@@ -25736,7 +25736,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="619" spans="1:14">
+    <row r="619" spans="1:14" hidden="1">
       <c r="A619" t="s">
         <v>292</v>
       </c>
@@ -25778,7 +25778,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="620" spans="1:14">
+    <row r="620" spans="1:14" hidden="1">
       <c r="A620" t="s">
         <v>292</v>
       </c>
@@ -25820,7 +25820,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="621" spans="1:14">
+    <row r="621" spans="1:14" hidden="1">
       <c r="A621" t="s">
         <v>296</v>
       </c>
@@ -25865,7 +25865,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="622" spans="1:14">
+    <row r="622" spans="1:14" hidden="1">
       <c r="A622" t="s">
         <v>296</v>
       </c>
@@ -25907,7 +25907,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="623" spans="1:14">
+    <row r="623" spans="1:14" hidden="1">
       <c r="A623" t="s">
         <v>296</v>
       </c>
@@ -25949,7 +25949,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="624" spans="1:14">
+    <row r="624" spans="1:14" hidden="1">
       <c r="A624" t="s">
         <v>296</v>
       </c>
@@ -25991,7 +25991,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="625" spans="1:14">
+    <row r="625" spans="1:14" hidden="1">
       <c r="A625" t="s">
         <v>296</v>
       </c>
@@ -26033,7 +26033,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="626" spans="1:14">
+    <row r="626" spans="1:14" hidden="1">
       <c r="A626" t="s">
         <v>296</v>
       </c>
@@ -26075,7 +26075,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="627" spans="1:14">
+    <row r="627" spans="1:14" hidden="1">
       <c r="A627" t="s">
         <v>296</v>
       </c>
@@ -26117,7 +26117,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="628" spans="1:14">
+    <row r="628" spans="1:14" hidden="1">
       <c r="A628" t="s">
         <v>296</v>
       </c>
@@ -26159,7 +26159,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="629" spans="1:14">
+    <row r="629" spans="1:14" hidden="1">
       <c r="A629" t="s">
         <v>296</v>
       </c>
@@ -26201,7 +26201,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="630" spans="1:14">
+    <row r="630" spans="1:14" hidden="1">
       <c r="A630" t="s">
         <v>296</v>
       </c>
@@ -26243,7 +26243,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="631" spans="1:14">
+    <row r="631" spans="1:14" hidden="1">
       <c r="A631" t="s">
         <v>296</v>
       </c>
@@ -26285,7 +26285,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="632" spans="1:14">
+    <row r="632" spans="1:14" hidden="1">
       <c r="A632" t="s">
         <v>296</v>
       </c>
@@ -26327,7 +26327,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="633" spans="1:14">
+    <row r="633" spans="1:14" hidden="1">
       <c r="A633" t="s">
         <v>296</v>
       </c>
@@ -26369,7 +26369,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="634" spans="1:14">
+    <row r="634" spans="1:14" hidden="1">
       <c r="A634" t="s">
         <v>306</v>
       </c>
@@ -26414,7 +26414,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="635" spans="1:14">
+    <row r="635" spans="1:14" hidden="1">
       <c r="A635" t="s">
         <v>306</v>
       </c>
@@ -26456,7 +26456,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="636" spans="1:14">
+    <row r="636" spans="1:14" hidden="1">
       <c r="A636" t="s">
         <v>306</v>
       </c>
@@ -26498,7 +26498,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="637" spans="1:14">
+    <row r="637" spans="1:14" hidden="1">
       <c r="A637" t="s">
         <v>306</v>
       </c>
@@ -26540,7 +26540,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="638" spans="1:14">
+    <row r="638" spans="1:14" hidden="1">
       <c r="A638" t="s">
         <v>306</v>
       </c>
@@ -26582,7 +26582,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="639" spans="1:14">
+    <row r="639" spans="1:14" hidden="1">
       <c r="A639" t="s">
         <v>306</v>
       </c>
@@ -26624,7 +26624,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="640" spans="1:14">
+    <row r="640" spans="1:14" hidden="1">
       <c r="A640" t="s">
         <v>306</v>
       </c>
@@ -26966,7 +26966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:14">
+    <row r="650" spans="1:14" hidden="1">
       <c r="A650" t="s">
         <v>312</v>
       </c>
@@ -27011,7 +27011,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="651" spans="1:14">
+    <row r="651" spans="1:14" hidden="1">
       <c r="A651" t="s">
         <v>312</v>
       </c>
@@ -27053,7 +27053,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="652" spans="1:14">
+    <row r="652" spans="1:14" hidden="1">
       <c r="A652" t="s">
         <v>312</v>
       </c>
@@ -27095,7 +27095,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="653" spans="1:14">
+    <row r="653" spans="1:14" hidden="1">
       <c r="A653" t="s">
         <v>312</v>
       </c>
@@ -27137,7 +27137,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="654" spans="1:14">
+    <row r="654" spans="1:14" hidden="1">
       <c r="A654" t="s">
         <v>312</v>
       </c>
@@ -27179,7 +27179,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="655" spans="1:14">
+    <row r="655" spans="1:14" hidden="1">
       <c r="A655" t="s">
         <v>312</v>
       </c>
@@ -27221,7 +27221,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="656" spans="1:14">
+    <row r="656" spans="1:14" hidden="1">
       <c r="A656" t="s">
         <v>312</v>
       </c>
@@ -27263,7 +27263,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="657" spans="1:14">
+    <row r="657" spans="1:14" hidden="1">
       <c r="A657" t="s">
         <v>313</v>
       </c>
@@ -27308,7 +27308,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="658" spans="1:14">
+    <row r="658" spans="1:14" hidden="1">
       <c r="A658" t="s">
         <v>313</v>
       </c>
@@ -27350,7 +27350,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="659" spans="1:14">
+    <row r="659" spans="1:14" hidden="1">
       <c r="A659" t="s">
         <v>313</v>
       </c>
@@ -27392,7 +27392,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="660" spans="1:14">
+    <row r="660" spans="1:14" hidden="1">
       <c r="A660" t="s">
         <v>313</v>
       </c>
@@ -27434,7 +27434,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="661" spans="1:14">
+    <row r="661" spans="1:14" hidden="1">
       <c r="A661" t="s">
         <v>313</v>
       </c>
@@ -27476,7 +27476,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="662" spans="1:14">
+    <row r="662" spans="1:14" hidden="1">
       <c r="A662" t="s">
         <v>313</v>
       </c>
@@ -27518,7 +27518,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="663" spans="1:14">
+    <row r="663" spans="1:14" hidden="1">
       <c r="A663" t="s">
         <v>316</v>
       </c>
@@ -27563,7 +27563,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="664" spans="1:14">
+    <row r="664" spans="1:14" hidden="1">
       <c r="A664" t="s">
         <v>316</v>
       </c>
@@ -27605,7 +27605,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="665" spans="1:14">
+    <row r="665" spans="1:14" hidden="1">
       <c r="A665" t="s">
         <v>316</v>
       </c>
@@ -27647,7 +27647,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="666" spans="1:14">
+    <row r="666" spans="1:14" hidden="1">
       <c r="A666" t="s">
         <v>316</v>
       </c>
@@ -27689,7 +27689,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="667" spans="1:14">
+    <row r="667" spans="1:14" hidden="1">
       <c r="A667" t="s">
         <v>316</v>
       </c>
@@ -27731,7 +27731,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="668" spans="1:14">
+    <row r="668" spans="1:14" hidden="1">
       <c r="A668" t="s">
         <v>316</v>
       </c>
@@ -27773,7 +27773,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="669" spans="1:14">
+    <row r="669" spans="1:14" hidden="1">
       <c r="A669" t="s">
         <v>318</v>
       </c>
@@ -27818,7 +27818,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="670" spans="1:14">
+    <row r="670" spans="1:14" hidden="1">
       <c r="A670" t="s">
         <v>318</v>
       </c>
@@ -27860,7 +27860,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="671" spans="1:14">
+    <row r="671" spans="1:14" hidden="1">
       <c r="A671" t="s">
         <v>318</v>
       </c>
@@ -27902,7 +27902,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="672" spans="1:14">
+    <row r="672" spans="1:14" hidden="1">
       <c r="A672" t="s">
         <v>318</v>
       </c>
@@ -27944,7 +27944,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="673" spans="1:14">
+    <row r="673" spans="1:14" hidden="1">
       <c r="A673" t="s">
         <v>318</v>
       </c>
@@ -27986,7 +27986,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="674" spans="1:14">
+    <row r="674" spans="1:14" hidden="1">
       <c r="A674" t="s">
         <v>318</v>
       </c>
@@ -28028,7 +28028,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="675" spans="1:14">
+    <row r="675" spans="1:14" hidden="1">
       <c r="A675" t="s">
         <v>318</v>
       </c>
@@ -28070,7 +28070,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="676" spans="1:14">
+    <row r="676" spans="1:14" hidden="1">
       <c r="A676" t="s">
         <v>318</v>
       </c>
@@ -28112,7 +28112,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="677" spans="1:14">
+    <row r="677" spans="1:14" hidden="1">
       <c r="A677" t="s">
         <v>318</v>
       </c>
@@ -28154,7 +28154,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="678" spans="1:14">
+    <row r="678" spans="1:14" hidden="1">
       <c r="A678" t="s">
         <v>318</v>
       </c>
@@ -28196,7 +28196,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="679" spans="1:14">
+    <row r="679" spans="1:14" hidden="1">
       <c r="A679" t="s">
         <v>318</v>
       </c>
@@ -28238,7 +28238,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="680" spans="1:14">
+    <row r="680" spans="1:14" hidden="1">
       <c r="A680" t="s">
         <v>318</v>
       </c>
@@ -28280,7 +28280,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="681" spans="1:14">
+    <row r="681" spans="1:14" hidden="1">
       <c r="A681" t="s">
         <v>318</v>
       </c>
@@ -28322,7 +28322,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="682" spans="1:14">
+    <row r="682" spans="1:14" hidden="1">
       <c r="A682" t="s">
         <v>320</v>
       </c>
@@ -28367,7 +28367,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="683" spans="1:14">
+    <row r="683" spans="1:14" hidden="1">
       <c r="A683" t="s">
         <v>320</v>
       </c>
@@ -28409,7 +28409,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="684" spans="1:14">
+    <row r="684" spans="1:14" hidden="1">
       <c r="A684" t="s">
         <v>320</v>
       </c>
@@ -28451,7 +28451,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="685" spans="1:14">
+    <row r="685" spans="1:14" hidden="1">
       <c r="A685" t="s">
         <v>320</v>
       </c>
@@ -28493,7 +28493,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="686" spans="1:14">
+    <row r="686" spans="1:14" hidden="1">
       <c r="A686" t="s">
         <v>320</v>
       </c>
@@ -28535,7 +28535,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="687" spans="1:14">
+    <row r="687" spans="1:14" hidden="1">
       <c r="A687" t="s">
         <v>320</v>
       </c>
@@ -28577,7 +28577,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="688" spans="1:14">
+    <row r="688" spans="1:14" hidden="1">
       <c r="A688" t="s">
         <v>320</v>
       </c>
@@ -28619,7 +28619,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="689" spans="1:14">
+    <row r="689" spans="1:14" hidden="1">
       <c r="A689" t="s">
         <v>320</v>
       </c>
@@ -28661,7 +28661,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="690" spans="1:14">
+    <row r="690" spans="1:14" hidden="1">
       <c r="A690" t="s">
         <v>320</v>
       </c>
@@ -28703,7 +28703,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="691" spans="1:14">
+    <row r="691" spans="1:14" hidden="1">
       <c r="A691" t="s">
         <v>320</v>
       </c>
@@ -28745,7 +28745,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="692" spans="1:14">
+    <row r="692" spans="1:14" hidden="1">
       <c r="A692" t="s">
         <v>320</v>
       </c>
@@ -28787,7 +28787,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="693" spans="1:14">
+    <row r="693" spans="1:14" hidden="1">
       <c r="A693" t="s">
         <v>320</v>
       </c>
@@ -28829,7 +28829,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="694" spans="1:14">
+    <row r="694" spans="1:14" hidden="1">
       <c r="A694" t="s">
         <v>320</v>
       </c>
@@ -28871,7 +28871,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="695" spans="1:14">
+    <row r="695" spans="1:14" hidden="1">
       <c r="A695" t="s">
         <v>320</v>
       </c>
@@ -28913,7 +28913,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="696" spans="1:14">
+    <row r="696" spans="1:14" hidden="1">
       <c r="A696" t="s">
         <v>320</v>
       </c>
@@ -28955,7 +28955,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="697" spans="1:14">
+    <row r="697" spans="1:14" hidden="1">
       <c r="A697" t="s">
         <v>320</v>
       </c>
@@ -28997,7 +28997,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="698" spans="1:14">
+    <row r="698" spans="1:14" hidden="1">
       <c r="A698" t="s">
         <v>331</v>
       </c>
@@ -29042,7 +29042,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="699" spans="1:14">
+    <row r="699" spans="1:14" hidden="1">
       <c r="A699" t="s">
         <v>331</v>
       </c>
@@ -29084,7 +29084,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="700" spans="1:14">
+    <row r="700" spans="1:14" hidden="1">
       <c r="A700" t="s">
         <v>331</v>
       </c>
@@ -29126,7 +29126,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="701" spans="1:14">
+    <row r="701" spans="1:14" hidden="1">
       <c r="A701" t="s">
         <v>331</v>
       </c>
@@ -29168,7 +29168,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="702" spans="1:14">
+    <row r="702" spans="1:14" hidden="1">
       <c r="A702" t="s">
         <v>331</v>
       </c>
@@ -29210,7 +29210,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="703" spans="1:14">
+    <row r="703" spans="1:14" hidden="1">
       <c r="A703" t="s">
         <v>331</v>
       </c>
@@ -29252,7 +29252,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="704" spans="1:14">
+    <row r="704" spans="1:14" hidden="1">
       <c r="A704" t="s">
         <v>331</v>
       </c>
@@ -29294,7 +29294,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="705" spans="1:14">
+    <row r="705" spans="1:14" hidden="1">
       <c r="A705" t="s">
         <v>331</v>
       </c>
@@ -29336,7 +29336,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="706" spans="1:14">
+    <row r="706" spans="1:14" hidden="1">
       <c r="A706" t="s">
         <v>331</v>
       </c>
@@ -29378,7 +29378,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="707" spans="1:14">
+    <row r="707" spans="1:14" hidden="1">
       <c r="A707" t="s">
         <v>331</v>
       </c>
@@ -29420,7 +29420,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="708" spans="1:14">
+    <row r="708" spans="1:14" hidden="1">
       <c r="A708" t="s">
         <v>331</v>
       </c>
@@ -29462,7 +29462,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="709" spans="1:14">
+    <row r="709" spans="1:14" hidden="1">
       <c r="A709" t="s">
         <v>331</v>
       </c>
@@ -29504,7 +29504,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="710" spans="1:14">
+    <row r="710" spans="1:14" hidden="1">
       <c r="A710" t="s">
         <v>331</v>
       </c>
@@ -29546,7 +29546,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="711" spans="1:14">
+    <row r="711" spans="1:14" hidden="1">
       <c r="A711" t="s">
         <v>331</v>
       </c>
@@ -29588,7 +29588,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="712" spans="1:14">
+    <row r="712" spans="1:14" hidden="1">
       <c r="A712" t="s">
         <v>331</v>
       </c>
@@ -29630,7 +29630,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="713" spans="1:14">
+    <row r="713" spans="1:14" hidden="1">
       <c r="A713" t="s">
         <v>331</v>
       </c>
@@ -29672,7 +29672,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="714" spans="1:14">
+    <row r="714" spans="1:14" hidden="1">
       <c r="A714" t="s">
         <v>331</v>
       </c>
@@ -29714,7 +29714,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="715" spans="1:14">
+    <row r="715" spans="1:14" hidden="1">
       <c r="A715" t="s">
         <v>331</v>
       </c>
@@ -29756,7 +29756,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="716" spans="1:14">
+    <row r="716" spans="1:14" hidden="1">
       <c r="A716" t="s">
         <v>331</v>
       </c>
@@ -29798,7 +29798,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="717" spans="1:14">
+    <row r="717" spans="1:14" hidden="1">
       <c r="A717" t="s">
         <v>331</v>
       </c>
@@ -29840,7 +29840,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="718" spans="1:14">
+    <row r="718" spans="1:14" hidden="1">
       <c r="A718" t="s">
         <v>331</v>
       </c>
@@ -29882,7 +29882,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="719" spans="1:14">
+    <row r="719" spans="1:14" hidden="1">
       <c r="A719" t="s">
         <v>331</v>
       </c>
@@ -29924,7 +29924,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="720" spans="1:14">
+    <row r="720" spans="1:14" hidden="1">
       <c r="A720" t="s">
         <v>331</v>
       </c>
@@ -29966,7 +29966,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="721" spans="1:14">
+    <row r="721" spans="1:14" hidden="1">
       <c r="A721" t="s">
         <v>331</v>
       </c>
@@ -30008,7 +30008,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="722" spans="1:14">
+    <row r="722" spans="1:14" hidden="1">
       <c r="A722" t="s">
         <v>331</v>
       </c>
@@ -30050,7 +30050,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="723" spans="1:14">
+    <row r="723" spans="1:14" hidden="1">
       <c r="A723" t="s">
         <v>353</v>
       </c>
@@ -30095,7 +30095,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="724" spans="1:14">
+    <row r="724" spans="1:14" hidden="1">
       <c r="A724" t="s">
         <v>353</v>
       </c>
@@ -30137,7 +30137,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="725" spans="1:14">
+    <row r="725" spans="1:14" hidden="1">
       <c r="A725" t="s">
         <v>353</v>
       </c>
@@ -30179,7 +30179,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="726" spans="1:14">
+    <row r="726" spans="1:14" hidden="1">
       <c r="A726" t="s">
         <v>353</v>
       </c>
@@ -30221,7 +30221,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="727" spans="1:14">
+    <row r="727" spans="1:14" hidden="1">
       <c r="A727" t="s">
         <v>353</v>
       </c>
@@ -30263,7 +30263,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="728" spans="1:14">
+    <row r="728" spans="1:14" hidden="1">
       <c r="A728" t="s">
         <v>353</v>
       </c>
@@ -30305,7 +30305,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="729" spans="1:14">
+    <row r="729" spans="1:14" hidden="1">
       <c r="A729" t="s">
         <v>353</v>
       </c>
@@ -30347,7 +30347,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="730" spans="1:14">
+    <row r="730" spans="1:14" hidden="1">
       <c r="A730" t="s">
         <v>353</v>
       </c>
@@ -30389,7 +30389,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="731" spans="1:14">
+    <row r="731" spans="1:14" hidden="1">
       <c r="A731" t="s">
         <v>353</v>
       </c>
@@ -30431,7 +30431,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="732" spans="1:14">
+    <row r="732" spans="1:14" hidden="1">
       <c r="A732" t="s">
         <v>353</v>
       </c>
@@ -30473,7 +30473,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="733" spans="1:14">
+    <row r="733" spans="1:14" hidden="1">
       <c r="A733" t="s">
         <v>353</v>
       </c>
@@ -30515,7 +30515,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="734" spans="1:14">
+    <row r="734" spans="1:14" hidden="1">
       <c r="A734" t="s">
         <v>356</v>
       </c>
@@ -30560,7 +30560,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="735" spans="1:14">
+    <row r="735" spans="1:14" hidden="1">
       <c r="A735" t="s">
         <v>356</v>
       </c>
@@ -30602,7 +30602,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="736" spans="1:14">
+    <row r="736" spans="1:14" hidden="1">
       <c r="A736" t="s">
         <v>356</v>
       </c>
@@ -30644,7 +30644,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="737" spans="1:14">
+    <row r="737" spans="1:14" hidden="1">
       <c r="A737" t="s">
         <v>356</v>
       </c>
@@ -30686,7 +30686,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="738" spans="1:14">
+    <row r="738" spans="1:14" hidden="1">
       <c r="A738" t="s">
         <v>356</v>
       </c>
@@ -30728,7 +30728,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="739" spans="1:14">
+    <row r="739" spans="1:14" hidden="1">
       <c r="A739" t="s">
         <v>356</v>
       </c>
@@ -30770,7 +30770,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="740" spans="1:14">
+    <row r="740" spans="1:14" hidden="1">
       <c r="A740" t="s">
         <v>356</v>
       </c>
@@ -30812,7 +30812,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="741" spans="1:14">
+    <row r="741" spans="1:14" hidden="1">
       <c r="A741" t="s">
         <v>356</v>
       </c>
@@ -30854,7 +30854,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="742" spans="1:14">
+    <row r="742" spans="1:14" hidden="1">
       <c r="A742" t="s">
         <v>356</v>
       </c>
@@ -30896,7 +30896,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="743" spans="1:14">
+    <row r="743" spans="1:14" hidden="1">
       <c r="A743" t="s">
         <v>356</v>
       </c>
@@ -30938,7 +30938,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="744" spans="1:14">
+    <row r="744" spans="1:14" hidden="1">
       <c r="A744" t="s">
         <v>356</v>
       </c>
@@ -30980,7 +30980,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="745" spans="1:14">
+    <row r="745" spans="1:14" hidden="1">
       <c r="A745" t="s">
         <v>356</v>
       </c>
@@ -31022,7 +31022,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="746" spans="1:14">
+    <row r="746" spans="1:14" hidden="1">
       <c r="A746" t="s">
         <v>356</v>
       </c>
@@ -31064,7 +31064,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="747" spans="1:14">
+    <row r="747" spans="1:14" hidden="1">
       <c r="A747" t="s">
         <v>359</v>
       </c>
@@ -31109,7 +31109,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="748" spans="1:14">
+    <row r="748" spans="1:14" hidden="1">
       <c r="A748" t="s">
         <v>359</v>
       </c>
@@ -31151,7 +31151,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="749" spans="1:14">
+    <row r="749" spans="1:14" hidden="1">
       <c r="A749" t="s">
         <v>359</v>
       </c>
@@ -31193,7 +31193,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="750" spans="1:14">
+    <row r="750" spans="1:14" hidden="1">
       <c r="A750" t="s">
         <v>359</v>
       </c>
@@ -31235,7 +31235,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="751" spans="1:14">
+    <row r="751" spans="1:14" hidden="1">
       <c r="A751" t="s">
         <v>359</v>
       </c>
@@ -31277,7 +31277,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="752" spans="1:14">
+    <row r="752" spans="1:14" hidden="1">
       <c r="A752" t="s">
         <v>359</v>
       </c>
@@ -31319,7 +31319,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="753" spans="1:14">
+    <row r="753" spans="1:14" hidden="1">
       <c r="A753" t="s">
         <v>359</v>
       </c>
@@ -31361,7 +31361,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="754" spans="1:14">
+    <row r="754" spans="1:14" hidden="1">
       <c r="A754" t="s">
         <v>359</v>
       </c>
@@ -31403,7 +31403,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="755" spans="1:14">
+    <row r="755" spans="1:14" hidden="1">
       <c r="A755" t="s">
         <v>359</v>
       </c>
@@ -31445,7 +31445,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="756" spans="1:14">
+    <row r="756" spans="1:14" hidden="1">
       <c r="A756" t="s">
         <v>359</v>
       </c>
@@ -31487,7 +31487,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="757" spans="1:14">
+    <row r="757" spans="1:14" hidden="1">
       <c r="A757" t="s">
         <v>359</v>
       </c>
@@ -31529,7 +31529,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="758" spans="1:14">
+    <row r="758" spans="1:14" hidden="1">
       <c r="A758" t="s">
         <v>359</v>
       </c>
@@ -31571,7 +31571,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="759" spans="1:14">
+    <row r="759" spans="1:14" hidden="1">
       <c r="A759" t="s">
         <v>359</v>
       </c>
@@ -31613,7 +31613,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="760" spans="1:14">
+    <row r="760" spans="1:14" hidden="1">
       <c r="A760" t="s">
         <v>359</v>
       </c>
@@ -31655,7 +31655,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="761" spans="1:14">
+    <row r="761" spans="1:14" hidden="1">
       <c r="A761" t="s">
         <v>359</v>
       </c>
@@ -31697,7 +31697,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="762" spans="1:14">
+    <row r="762" spans="1:14" hidden="1">
       <c r="A762" t="s">
         <v>359</v>
       </c>
@@ -31739,7 +31739,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="763" spans="1:14">
+    <row r="763" spans="1:14" hidden="1">
       <c r="A763" t="s">
         <v>359</v>
       </c>
@@ -31781,7 +31781,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="764" spans="1:14">
+    <row r="764" spans="1:14" hidden="1">
       <c r="A764" t="s">
         <v>359</v>
       </c>
@@ -31823,7 +31823,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="765" spans="1:14">
+    <row r="765" spans="1:14" hidden="1">
       <c r="A765" t="s">
         <v>359</v>
       </c>
@@ -32231,7 +32231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="777" spans="1:12">
+    <row r="777" spans="1:12" hidden="1">
       <c r="A777" t="s">
         <v>374</v>
       </c>
@@ -32270,7 +32270,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="778" spans="1:12">
+    <row r="778" spans="1:12" hidden="1">
       <c r="A778" t="s">
         <v>374</v>
       </c>
@@ -32306,7 +32306,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="779" spans="1:12">
+    <row r="779" spans="1:12" hidden="1">
       <c r="A779" t="s">
         <v>374</v>
       </c>
@@ -32342,7 +32342,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="780" spans="1:12">
+    <row r="780" spans="1:12" hidden="1">
       <c r="A780" t="s">
         <v>374</v>
       </c>
@@ -32378,7 +32378,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="781" spans="1:12">
+    <row r="781" spans="1:12" hidden="1">
       <c r="A781" t="s">
         <v>374</v>
       </c>
@@ -32414,7 +32414,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="782" spans="1:12">
+    <row r="782" spans="1:12" hidden="1">
       <c r="A782" t="s">
         <v>374</v>
       </c>
@@ -32450,7 +32450,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="783" spans="1:12">
+    <row r="783" spans="1:12" hidden="1">
       <c r="A783" t="s">
         <v>374</v>
       </c>
@@ -32486,7 +32486,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="784" spans="1:12">
+    <row r="784" spans="1:12" hidden="1">
       <c r="A784" t="s">
         <v>374</v>
       </c>
@@ -32522,7 +32522,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="785" spans="1:12">
+    <row r="785" spans="1:12" hidden="1">
       <c r="A785" t="s">
         <v>374</v>
       </c>
@@ -32558,7 +32558,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="786" spans="1:12">
+    <row r="786" spans="1:12" hidden="1">
       <c r="A786" t="s">
         <v>374</v>
       </c>
@@ -32594,7 +32594,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="787" spans="1:12">
+    <row r="787" spans="1:12" hidden="1">
       <c r="A787" t="s">
         <v>374</v>
       </c>
@@ -32630,7 +32630,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="788" spans="1:12">
+    <row r="788" spans="1:12" hidden="1">
       <c r="A788" t="s">
         <v>374</v>
       </c>
@@ -32666,7 +32666,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="789" spans="1:12">
+    <row r="789" spans="1:12" hidden="1">
       <c r="A789" t="s">
         <v>374</v>
       </c>
@@ -32702,7 +32702,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="790" spans="1:12">
+    <row r="790" spans="1:12" hidden="1">
       <c r="A790" t="s">
         <v>374</v>
       </c>
@@ -32738,7 +32738,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="791" spans="1:12">
+    <row r="791" spans="1:12" hidden="1">
       <c r="A791" t="s">
         <v>374</v>
       </c>
@@ -32774,7 +32774,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="792" spans="1:12">
+    <row r="792" spans="1:12" hidden="1">
       <c r="A792" t="s">
         <v>374</v>
       </c>
@@ -32810,7 +32810,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="793" spans="1:12">
+    <row r="793" spans="1:12" hidden="1">
       <c r="A793" t="s">
         <v>374</v>
       </c>
@@ -32846,7 +32846,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="794" spans="1:12">
+    <row r="794" spans="1:12" hidden="1">
       <c r="A794" t="s">
         <v>374</v>
       </c>
@@ -32882,7 +32882,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="795" spans="1:12">
+    <row r="795" spans="1:12" hidden="1">
       <c r="A795" t="s">
         <v>374</v>
       </c>
@@ -32918,7 +32918,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="796" spans="1:12">
+    <row r="796" spans="1:12" hidden="1">
       <c r="A796" t="s">
         <v>374</v>
       </c>
@@ -32954,7 +32954,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="797" spans="1:12">
+    <row r="797" spans="1:12" hidden="1">
       <c r="A797" t="s">
         <v>374</v>
       </c>
@@ -32990,7 +32990,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="798" spans="1:12">
+    <row r="798" spans="1:12" hidden="1">
       <c r="A798" t="s">
         <v>374</v>
       </c>
@@ -33026,7 +33026,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="799" spans="1:12">
+    <row r="799" spans="1:12" hidden="1">
       <c r="A799" t="s">
         <v>374</v>
       </c>
@@ -33062,7 +33062,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="800" spans="1:12">
+    <row r="800" spans="1:12" hidden="1">
       <c r="A800" t="s">
         <v>374</v>
       </c>
@@ -33098,7 +33098,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="801" spans="1:12">
+    <row r="801" spans="1:12" hidden="1">
       <c r="A801" t="s">
         <v>374</v>
       </c>
@@ -33134,7 +33134,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="802" spans="1:12">
+    <row r="802" spans="1:12" hidden="1">
       <c r="A802" t="s">
         <v>374</v>
       </c>
@@ -33170,7 +33170,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="803" spans="1:12">
+    <row r="803" spans="1:12" hidden="1">
       <c r="A803" t="s">
         <v>374</v>
       </c>
@@ -33206,7 +33206,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="804" spans="1:12">
+    <row r="804" spans="1:12" hidden="1">
       <c r="A804" t="s">
         <v>374</v>
       </c>
@@ -33641,7 +33641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="817" spans="1:12">
+    <row r="817" spans="1:12" hidden="1">
       <c r="A817" t="s">
         <v>395</v>
       </c>
@@ -33680,7 +33680,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="818" spans="1:12">
+    <row r="818" spans="1:12" hidden="1">
       <c r="A818" t="s">
         <v>395</v>
       </c>
@@ -33716,7 +33716,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="819" spans="1:12">
+    <row r="819" spans="1:12" hidden="1">
       <c r="A819" t="s">
         <v>395</v>
       </c>
@@ -33752,7 +33752,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="820" spans="1:12">
+    <row r="820" spans="1:12" hidden="1">
       <c r="A820" t="s">
         <v>395</v>
       </c>
@@ -33788,7 +33788,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="821" spans="1:12">
+    <row r="821" spans="1:12" hidden="1">
       <c r="A821" t="s">
         <v>395</v>
       </c>
@@ -33824,7 +33824,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="822" spans="1:12">
+    <row r="822" spans="1:12" hidden="1">
       <c r="A822" t="s">
         <v>395</v>
       </c>
@@ -33860,7 +33860,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="823" spans="1:12">
+    <row r="823" spans="1:12" hidden="1">
       <c r="A823" t="s">
         <v>395</v>
       </c>
@@ -33896,7 +33896,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="824" spans="1:12">
+    <row r="824" spans="1:12" hidden="1">
       <c r="A824" t="s">
         <v>395</v>
       </c>
@@ -33932,7 +33932,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="825" spans="1:12">
+    <row r="825" spans="1:12" hidden="1">
       <c r="A825" t="s">
         <v>395</v>
       </c>
@@ -33968,7 +33968,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="826" spans="1:12">
+    <row r="826" spans="1:12" hidden="1">
       <c r="A826" t="s">
         <v>395</v>
       </c>
@@ -34004,7 +34004,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="827" spans="1:12">
+    <row r="827" spans="1:12" hidden="1">
       <c r="A827" t="s">
         <v>395</v>
       </c>
@@ -34040,7 +34040,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="828" spans="1:12">
+    <row r="828" spans="1:12" hidden="1">
       <c r="A828" t="s">
         <v>395</v>
       </c>
@@ -34076,7 +34076,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="829" spans="1:12">
+    <row r="829" spans="1:12" hidden="1">
       <c r="A829" t="s">
         <v>395</v>
       </c>
@@ -34112,7 +34112,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="830" spans="1:12">
+    <row r="830" spans="1:12" hidden="1">
       <c r="A830" t="s">
         <v>395</v>
       </c>
@@ -34148,7 +34148,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="831" spans="1:12">
+    <row r="831" spans="1:12" hidden="1">
       <c r="A831" t="s">
         <v>395</v>
       </c>
@@ -34184,7 +34184,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="832" spans="1:12">
+    <row r="832" spans="1:12" hidden="1">
       <c r="A832" t="s">
         <v>395</v>
       </c>
@@ -34220,7 +34220,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="833" spans="1:14">
+    <row r="833" spans="1:14" hidden="1">
       <c r="A833" t="s">
         <v>395</v>
       </c>
@@ -34256,7 +34256,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="834" spans="1:14">
+    <row r="834" spans="1:14" hidden="1">
       <c r="A834" t="s">
         <v>395</v>
       </c>
@@ -34292,7 +34292,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="835" spans="1:14">
+    <row r="835" spans="1:14" hidden="1">
       <c r="A835" t="s">
         <v>395</v>
       </c>
@@ -34328,7 +34328,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="836" spans="1:14">
+    <row r="836" spans="1:14" hidden="1">
       <c r="A836" t="s">
         <v>395</v>
       </c>
@@ -34364,7 +34364,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="837" spans="1:14">
+    <row r="837" spans="1:14" hidden="1">
       <c r="A837" t="s">
         <v>397</v>
       </c>
@@ -34403,7 +34403,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="838" spans="1:14">
+    <row r="838" spans="1:14" hidden="1">
       <c r="A838" t="s">
         <v>397</v>
       </c>
@@ -34439,7 +34439,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="839" spans="1:14">
+    <row r="839" spans="1:14" hidden="1">
       <c r="A839" t="s">
         <v>397</v>
       </c>
@@ -34475,7 +34475,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="840" spans="1:14">
+    <row r="840" spans="1:14" hidden="1">
       <c r="A840" t="s">
         <v>397</v>
       </c>
@@ -34511,7 +34511,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="841" spans="1:14">
+    <row r="841" spans="1:14" hidden="1">
       <c r="A841" t="s">
         <v>397</v>
       </c>
@@ -34547,7 +34547,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="842" spans="1:14">
+    <row r="842" spans="1:14" hidden="1">
       <c r="A842" t="s">
         <v>397</v>
       </c>
@@ -34583,7 +34583,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="843" spans="1:14">
+    <row r="843" spans="1:14" hidden="1">
       <c r="A843" t="s">
         <v>397</v>
       </c>
@@ -34619,7 +34619,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="844" spans="1:14">
+    <row r="844" spans="1:14" hidden="1">
       <c r="A844" t="s">
         <v>397</v>
       </c>
@@ -34655,7 +34655,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="845" spans="1:14">
+    <row r="845" spans="1:14" hidden="1">
       <c r="A845" t="s">
         <v>399</v>
       </c>
@@ -34700,7 +34700,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="846" spans="1:14">
+    <row r="846" spans="1:14" hidden="1">
       <c r="A846" t="s">
         <v>399</v>
       </c>
@@ -34742,7 +34742,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="847" spans="1:14">
+    <row r="847" spans="1:14" hidden="1">
       <c r="A847" t="s">
         <v>399</v>
       </c>
@@ -34784,7 +34784,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="848" spans="1:14">
+    <row r="848" spans="1:14" hidden="1">
       <c r="A848" t="s">
         <v>399</v>
       </c>
@@ -34826,7 +34826,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="849" spans="1:14">
+    <row r="849" spans="1:14" hidden="1">
       <c r="A849" t="s">
         <v>399</v>
       </c>
@@ -34868,7 +34868,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="850" spans="1:14">
+    <row r="850" spans="1:14" hidden="1">
       <c r="A850" t="s">
         <v>399</v>
       </c>
@@ -34910,7 +34910,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="851" spans="1:14">
+    <row r="851" spans="1:14" hidden="1">
       <c r="A851" t="s">
         <v>399</v>
       </c>
@@ -34952,7 +34952,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="852" spans="1:14">
+    <row r="852" spans="1:14" hidden="1">
       <c r="A852" t="s">
         <v>399</v>
       </c>
@@ -34994,7 +34994,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="853" spans="1:14">
+    <row r="853" spans="1:14" hidden="1">
       <c r="A853" t="s">
         <v>399</v>
       </c>
@@ -35036,7 +35036,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="854" spans="1:14">
+    <row r="854" spans="1:14" hidden="1">
       <c r="A854" t="s">
         <v>399</v>
       </c>
@@ -35078,7 +35078,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="855" spans="1:14">
+    <row r="855" spans="1:14" hidden="1">
       <c r="A855" t="s">
         <v>399</v>
       </c>
@@ -35120,7 +35120,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="856" spans="1:14">
+    <row r="856" spans="1:14" hidden="1">
       <c r="A856" t="s">
         <v>399</v>
       </c>
@@ -35162,7 +35162,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="857" spans="1:14">
+    <row r="857" spans="1:14" hidden="1">
       <c r="A857" t="s">
         <v>399</v>
       </c>
@@ -35204,7 +35204,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="858" spans="1:14">
+    <row r="858" spans="1:14" hidden="1">
       <c r="A858" t="s">
         <v>399</v>
       </c>
@@ -35246,7 +35246,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="859" spans="1:14">
+    <row r="859" spans="1:14" hidden="1">
       <c r="A859" t="s">
         <v>399</v>
       </c>
@@ -35288,7 +35288,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="860" spans="1:14">
+    <row r="860" spans="1:14" hidden="1">
       <c r="A860" t="s">
         <v>399</v>
       </c>
@@ -35330,7 +35330,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="861" spans="1:14">
+    <row r="861" spans="1:14" hidden="1">
       <c r="A861" t="s">
         <v>399</v>
       </c>
@@ -35372,7 +35372,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="862" spans="1:14">
+    <row r="862" spans="1:14" hidden="1">
       <c r="A862" t="s">
         <v>399</v>
       </c>
@@ -35414,7 +35414,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="863" spans="1:14">
+    <row r="863" spans="1:14" hidden="1">
       <c r="A863" t="s">
         <v>399</v>
       </c>
@@ -35456,7 +35456,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="864" spans="1:14">
+    <row r="864" spans="1:14" hidden="1">
       <c r="A864" t="s">
         <v>399</v>
       </c>
@@ -35498,7 +35498,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="865" spans="1:14">
+    <row r="865" spans="1:14" hidden="1">
       <c r="A865" t="s">
         <v>399</v>
       </c>
@@ -35540,7 +35540,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="866" spans="1:14">
+    <row r="866" spans="1:14" hidden="1">
       <c r="A866" t="s">
         <v>399</v>
       </c>
@@ -35582,7 +35582,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="867" spans="1:14">
+    <row r="867" spans="1:14" hidden="1">
       <c r="A867" t="s">
         <v>399</v>
       </c>
@@ -35624,7 +35624,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="868" spans="1:14">
+    <row r="868" spans="1:14" hidden="1">
       <c r="A868" t="s">
         <v>399</v>
       </c>
@@ -35666,7 +35666,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="869" spans="1:14">
+    <row r="869" spans="1:14" hidden="1">
       <c r="A869" t="s">
         <v>399</v>
       </c>
@@ -35708,7 +35708,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="870" spans="1:14">
+    <row r="870" spans="1:14" hidden="1">
       <c r="A870" t="s">
         <v>412</v>
       </c>
@@ -35747,7 +35747,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="871" spans="1:14">
+    <row r="871" spans="1:14" hidden="1">
       <c r="A871" t="s">
         <v>412</v>
       </c>
@@ -35783,7 +35783,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="872" spans="1:14">
+    <row r="872" spans="1:14" hidden="1">
       <c r="A872" t="s">
         <v>412</v>
       </c>
@@ -35819,7 +35819,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="873" spans="1:14">
+    <row r="873" spans="1:14" hidden="1">
       <c r="A873" t="s">
         <v>412</v>
       </c>
@@ -35855,7 +35855,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="874" spans="1:14">
+    <row r="874" spans="1:14" hidden="1">
       <c r="A874" t="s">
         <v>412</v>
       </c>
@@ -35891,7 +35891,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="875" spans="1:14">
+    <row r="875" spans="1:14" hidden="1">
       <c r="A875" t="s">
         <v>412</v>
       </c>
@@ -35927,7 +35927,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="876" spans="1:14">
+    <row r="876" spans="1:14" hidden="1">
       <c r="A876" t="s">
         <v>412</v>
       </c>
@@ -35963,7 +35963,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="877" spans="1:14">
+    <row r="877" spans="1:14" hidden="1">
       <c r="A877" t="s">
         <v>412</v>
       </c>
@@ -35999,7 +35999,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="878" spans="1:14">
+    <row r="878" spans="1:14" hidden="1">
       <c r="A878" t="s">
         <v>412</v>
       </c>
@@ -36035,7 +36035,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="879" spans="1:14">
+    <row r="879" spans="1:14" hidden="1">
       <c r="A879" t="s">
         <v>412</v>
       </c>
@@ -36071,7 +36071,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="880" spans="1:14">
+    <row r="880" spans="1:14" hidden="1">
       <c r="A880" t="s">
         <v>412</v>
       </c>
@@ -36107,7 +36107,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="881" spans="1:12">
+    <row r="881" spans="1:12" hidden="1">
       <c r="A881" t="s">
         <v>412</v>
       </c>
@@ -36143,7 +36143,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="882" spans="1:12">
+    <row r="882" spans="1:12" hidden="1">
       <c r="A882" t="s">
         <v>412</v>
       </c>
@@ -36179,7 +36179,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="883" spans="1:12">
+    <row r="883" spans="1:12" hidden="1">
       <c r="A883" t="s">
         <v>412</v>
       </c>
@@ -36215,7 +36215,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="884" spans="1:12">
+    <row r="884" spans="1:12" hidden="1">
       <c r="A884" t="s">
         <v>418</v>
       </c>
@@ -36254,7 +36254,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="885" spans="1:12">
+    <row r="885" spans="1:12" hidden="1">
       <c r="A885" t="s">
         <v>418</v>
       </c>
@@ -36290,7 +36290,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="886" spans="1:12">
+    <row r="886" spans="1:12" hidden="1">
       <c r="A886" t="s">
         <v>418</v>
       </c>
@@ -36326,7 +36326,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="887" spans="1:12">
+    <row r="887" spans="1:12" hidden="1">
       <c r="A887" t="s">
         <v>418</v>
       </c>
@@ -36362,7 +36362,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="888" spans="1:12">
+    <row r="888" spans="1:12" hidden="1">
       <c r="A888" t="s">
         <v>418</v>
       </c>
@@ -36398,7 +36398,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="889" spans="1:12">
+    <row r="889" spans="1:12" hidden="1">
       <c r="A889" t="s">
         <v>418</v>
       </c>
@@ -36434,7 +36434,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="890" spans="1:12">
+    <row r="890" spans="1:12" hidden="1">
       <c r="A890" t="s">
         <v>418</v>
       </c>
@@ -36470,7 +36470,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="891" spans="1:12">
+    <row r="891" spans="1:12" hidden="1">
       <c r="A891" t="s">
         <v>418</v>
       </c>
@@ -36506,7 +36506,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="892" spans="1:12">
+    <row r="892" spans="1:12" hidden="1">
       <c r="A892" t="s">
         <v>418</v>
       </c>
@@ -36542,7 +36542,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="893" spans="1:12">
+    <row r="893" spans="1:12" hidden="1">
       <c r="A893" t="s">
         <v>418</v>
       </c>
@@ -36578,7 +36578,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="894" spans="1:12">
+    <row r="894" spans="1:12" hidden="1">
       <c r="A894" t="s">
         <v>418</v>
       </c>
@@ -36614,7 +36614,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="895" spans="1:12">
+    <row r="895" spans="1:12" hidden="1">
       <c r="A895" t="s">
         <v>418</v>
       </c>
@@ -36650,7 +36650,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="896" spans="1:12">
+    <row r="896" spans="1:12" hidden="1">
       <c r="A896" t="s">
         <v>418</v>
       </c>
@@ -36686,7 +36686,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="897" spans="1:12">
+    <row r="897" spans="1:12" hidden="1">
       <c r="A897" t="s">
         <v>418</v>
       </c>
@@ -36722,7 +36722,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="898" spans="1:12">
+    <row r="898" spans="1:12" hidden="1">
       <c r="A898" t="s">
         <v>418</v>
       </c>
@@ -36758,7 +36758,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="899" spans="1:12">
+    <row r="899" spans="1:12" hidden="1">
       <c r="A899" t="s">
         <v>418</v>
       </c>
@@ -36794,7 +36794,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="900" spans="1:12">
+    <row r="900" spans="1:12" hidden="1">
       <c r="A900" t="s">
         <v>418</v>
       </c>
@@ -47903,7 +47903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1234" spans="1:12">
+    <row r="1234" spans="1:12" hidden="1">
       <c r="A1234" t="s">
         <v>536</v>
       </c>
@@ -47942,7 +47942,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="1235" spans="1:12">
+    <row r="1235" spans="1:12" hidden="1">
       <c r="A1235" t="s">
         <v>536</v>
       </c>
@@ -47978,7 +47978,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="1236" spans="1:12">
+    <row r="1236" spans="1:12" hidden="1">
       <c r="A1236" t="s">
         <v>536</v>
       </c>
@@ -48014,7 +48014,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="1237" spans="1:12">
+    <row r="1237" spans="1:12" hidden="1">
       <c r="A1237" t="s">
         <v>536</v>
       </c>
@@ -48050,7 +48050,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="1238" spans="1:12">
+    <row r="1238" spans="1:12" hidden="1">
       <c r="A1238" t="s">
         <v>536</v>
       </c>
@@ -48086,7 +48086,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="1239" spans="1:12">
+    <row r="1239" spans="1:12" hidden="1">
       <c r="A1239" t="s">
         <v>536</v>
       </c>
@@ -48122,7 +48122,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="1240" spans="1:12">
+    <row r="1240" spans="1:12" hidden="1">
       <c r="A1240" t="s">
         <v>536</v>
       </c>
@@ -48158,7 +48158,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="1241" spans="1:12">
+    <row r="1241" spans="1:12" hidden="1">
       <c r="A1241" t="s">
         <v>536</v>
       </c>
@@ -48194,7 +48194,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="1242" spans="1:12">
+    <row r="1242" spans="1:12" hidden="1">
       <c r="A1242" t="s">
         <v>536</v>
       </c>
@@ -48230,7 +48230,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="1243" spans="1:12">
+    <row r="1243" spans="1:12" hidden="1">
       <c r="A1243" t="s">
         <v>536</v>
       </c>
@@ -48266,7 +48266,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="1244" spans="1:12">
+    <row r="1244" spans="1:12" hidden="1">
       <c r="A1244" t="s">
         <v>539</v>
       </c>
@@ -48305,7 +48305,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="1245" spans="1:12">
+    <row r="1245" spans="1:12" hidden="1">
       <c r="A1245" t="s">
         <v>539</v>
       </c>
@@ -48341,7 +48341,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="1246" spans="1:12">
+    <row r="1246" spans="1:12" hidden="1">
       <c r="A1246" t="s">
         <v>539</v>
       </c>
@@ -48377,7 +48377,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="1247" spans="1:12">
+    <row r="1247" spans="1:12" hidden="1">
       <c r="A1247" t="s">
         <v>539</v>
       </c>
@@ -48413,7 +48413,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="1248" spans="1:12">
+    <row r="1248" spans="1:12" hidden="1">
       <c r="A1248" t="s">
         <v>539</v>
       </c>
@@ -48449,7 +48449,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="1249" spans="1:14">
+    <row r="1249" spans="1:14" hidden="1">
       <c r="A1249" t="s">
         <v>539</v>
       </c>
@@ -48485,7 +48485,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="1250" spans="1:14">
+    <row r="1250" spans="1:14" hidden="1">
       <c r="A1250" t="s">
         <v>539</v>
       </c>
@@ -48521,7 +48521,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="1251" spans="1:14">
+    <row r="1251" spans="1:14" hidden="1">
       <c r="A1251" t="s">
         <v>539</v>
       </c>
@@ -48557,7 +48557,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="1252" spans="1:14">
+    <row r="1252" spans="1:14" hidden="1">
       <c r="A1252" t="s">
         <v>539</v>
       </c>
@@ -48593,7 +48593,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="1253" spans="1:14">
+    <row r="1253" spans="1:14" hidden="1">
       <c r="A1253" t="s">
         <v>539</v>
       </c>
@@ -48629,7 +48629,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="1254" spans="1:14">
+    <row r="1254" spans="1:14" hidden="1">
       <c r="A1254" t="s">
         <v>541</v>
       </c>
@@ -48668,7 +48668,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1255" spans="1:14">
+    <row r="1255" spans="1:14" hidden="1">
       <c r="A1255" t="s">
         <v>541</v>
       </c>
@@ -48704,7 +48704,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1256" spans="1:14">
+    <row r="1256" spans="1:14" hidden="1">
       <c r="A1256" t="s">
         <v>541</v>
       </c>
@@ -48740,7 +48740,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1257" spans="1:14">
+    <row r="1257" spans="1:14" hidden="1">
       <c r="A1257" t="s">
         <v>541</v>
       </c>
@@ -48776,7 +48776,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1258" spans="1:14">
+    <row r="1258" spans="1:14" hidden="1">
       <c r="A1258" t="s">
         <v>541</v>
       </c>
@@ -48812,7 +48812,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1259" spans="1:14">
+    <row r="1259" spans="1:14" hidden="1">
       <c r="A1259" t="s">
         <v>541</v>
       </c>
@@ -48848,7 +48848,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1260" spans="1:14">
+    <row r="1260" spans="1:14" hidden="1">
       <c r="A1260" t="s">
         <v>541</v>
       </c>
@@ -48884,7 +48884,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1261" spans="1:14">
+    <row r="1261" spans="1:14" hidden="1">
       <c r="A1261" t="s">
         <v>541</v>
       </c>
@@ -48920,7 +48920,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1262" spans="1:14">
+    <row r="1262" spans="1:14" hidden="1">
       <c r="A1262" t="s">
         <v>541</v>
       </c>
@@ -48956,7 +48956,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="1263" spans="1:14">
+    <row r="1263" spans="1:14" hidden="1">
       <c r="A1263" t="s">
         <v>543</v>
       </c>
@@ -49001,7 +49001,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1264" spans="1:14">
+    <row r="1264" spans="1:14" hidden="1">
       <c r="A1264" t="s">
         <v>543</v>
       </c>
@@ -49043,7 +49043,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1265" spans="1:14">
+    <row r="1265" spans="1:14" hidden="1">
       <c r="A1265" t="s">
         <v>543</v>
       </c>
@@ -49085,7 +49085,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1266" spans="1:14">
+    <row r="1266" spans="1:14" hidden="1">
       <c r="A1266" t="s">
         <v>543</v>
       </c>
@@ -49127,7 +49127,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1267" spans="1:14">
+    <row r="1267" spans="1:14" hidden="1">
       <c r="A1267" t="s">
         <v>543</v>
       </c>
@@ -49169,7 +49169,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1268" spans="1:14">
+    <row r="1268" spans="1:14" hidden="1">
       <c r="A1268" t="s">
         <v>543</v>
       </c>
@@ -49211,7 +49211,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1269" spans="1:14">
+    <row r="1269" spans="1:14" hidden="1">
       <c r="A1269" t="s">
         <v>545</v>
       </c>
@@ -49256,7 +49256,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1270" spans="1:14">
+    <row r="1270" spans="1:14" hidden="1">
       <c r="A1270" t="s">
         <v>545</v>
       </c>
@@ -49298,7 +49298,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1271" spans="1:14">
+    <row r="1271" spans="1:14" hidden="1">
       <c r="A1271" t="s">
         <v>545</v>
       </c>
@@ -49340,7 +49340,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1272" spans="1:14">
+    <row r="1272" spans="1:14" hidden="1">
       <c r="A1272" t="s">
         <v>545</v>
       </c>
@@ -49382,7 +49382,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1273" spans="1:14">
+    <row r="1273" spans="1:14" hidden="1">
       <c r="A1273" t="s">
         <v>545</v>
       </c>
@@ -49424,7 +49424,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1274" spans="1:14">
+    <row r="1274" spans="1:14" hidden="1">
       <c r="A1274" t="s">
         <v>545</v>
       </c>
@@ -49466,7 +49466,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1275" spans="1:14">
+    <row r="1275" spans="1:14" hidden="1">
       <c r="A1275" t="s">
         <v>545</v>
       </c>
@@ -49508,7 +49508,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1276" spans="1:14">
+    <row r="1276" spans="1:14" hidden="1">
       <c r="A1276" t="s">
         <v>545</v>
       </c>
@@ -52703,7 +52703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1372" spans="1:14">
+    <row r="1372" spans="1:14" hidden="1">
       <c r="A1372" t="s">
         <v>577</v>
       </c>
@@ -52748,7 +52748,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1373" spans="1:14">
+    <row r="1373" spans="1:14" hidden="1">
       <c r="A1373" t="s">
         <v>577</v>
       </c>
@@ -52790,7 +52790,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1374" spans="1:14">
+    <row r="1374" spans="1:14" hidden="1">
       <c r="A1374" t="s">
         <v>577</v>
       </c>
@@ -52832,7 +52832,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1375" spans="1:14">
+    <row r="1375" spans="1:14" hidden="1">
       <c r="A1375" t="s">
         <v>577</v>
       </c>
@@ -52874,7 +52874,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1376" spans="1:14">
+    <row r="1376" spans="1:14" hidden="1">
       <c r="A1376" t="s">
         <v>577</v>
       </c>
@@ -52916,7 +52916,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1377" spans="1:14">
+    <row r="1377" spans="1:14" hidden="1">
       <c r="A1377" t="s">
         <v>577</v>
       </c>
@@ -52958,7 +52958,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1378" spans="1:14">
+    <row r="1378" spans="1:14" hidden="1">
       <c r="A1378" t="s">
         <v>577</v>
       </c>
@@ -53000,7 +53000,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1379" spans="1:14">
+    <row r="1379" spans="1:14" hidden="1">
       <c r="A1379" t="s">
         <v>577</v>
       </c>
@@ -53042,7 +53042,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1380" spans="1:14">
+    <row r="1380" spans="1:14" hidden="1">
       <c r="A1380" t="s">
         <v>577</v>
       </c>
@@ -53084,7 +53084,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1381" spans="1:14">
+    <row r="1381" spans="1:14" hidden="1">
       <c r="A1381" t="s">
         <v>577</v>
       </c>
@@ -53126,7 +53126,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1382" spans="1:14">
+    <row r="1382" spans="1:14" hidden="1">
       <c r="A1382" t="s">
         <v>577</v>
       </c>
@@ -53168,7 +53168,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1383" spans="1:14">
+    <row r="1383" spans="1:14" hidden="1">
       <c r="A1383" t="s">
         <v>577</v>
       </c>
@@ -53210,7 +53210,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1384" spans="1:14">
+    <row r="1384" spans="1:14" hidden="1">
       <c r="A1384" t="s">
         <v>577</v>
       </c>
@@ -53252,7 +53252,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1385" spans="1:14">
+    <row r="1385" spans="1:14" hidden="1">
       <c r="A1385" t="s">
         <v>577</v>
       </c>
@@ -53294,7 +53294,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1386" spans="1:14">
+    <row r="1386" spans="1:14" hidden="1">
       <c r="A1386" t="s">
         <v>577</v>
       </c>
@@ -53336,7 +53336,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1387" spans="1:14">
+    <row r="1387" spans="1:14" hidden="1">
       <c r="A1387" t="s">
         <v>577</v>
       </c>
@@ -53378,7 +53378,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1388" spans="1:14">
+    <row r="1388" spans="1:14" hidden="1">
       <c r="A1388" t="s">
         <v>577</v>
       </c>
@@ -53420,7 +53420,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1389" spans="1:14">
+    <row r="1389" spans="1:14" hidden="1">
       <c r="A1389" t="s">
         <v>577</v>
       </c>
@@ -53462,7 +53462,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1390" spans="1:14">
+    <row r="1390" spans="1:14" hidden="1">
       <c r="A1390" t="s">
         <v>577</v>
       </c>
@@ -53504,7 +53504,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1391" spans="1:14">
+    <row r="1391" spans="1:14" hidden="1">
       <c r="A1391" t="s">
         <v>577</v>
       </c>
@@ -53546,7 +53546,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1392" spans="1:14">
+    <row r="1392" spans="1:14" hidden="1">
       <c r="A1392" t="s">
         <v>577</v>
       </c>
@@ -53588,7 +53588,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1393" spans="1:14">
+    <row r="1393" spans="1:14" hidden="1">
       <c r="A1393" t="s">
         <v>577</v>
       </c>
@@ -53630,7 +53630,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1394" spans="1:14">
+    <row r="1394" spans="1:14" hidden="1">
       <c r="A1394" t="s">
         <v>577</v>
       </c>
@@ -53672,7 +53672,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1395" spans="1:14">
+    <row r="1395" spans="1:14" hidden="1">
       <c r="A1395" t="s">
         <v>577</v>
       </c>
@@ -53714,7 +53714,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1396" spans="1:14">
+    <row r="1396" spans="1:14" hidden="1">
       <c r="A1396" t="s">
         <v>577</v>
       </c>
@@ -53756,7 +53756,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1397" spans="1:14">
+    <row r="1397" spans="1:14" hidden="1">
       <c r="A1397" t="s">
         <v>577</v>
       </c>
@@ -53798,7 +53798,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1398" spans="1:14">
+    <row r="1398" spans="1:14" hidden="1">
       <c r="A1398" t="s">
         <v>577</v>
       </c>
@@ -53840,7 +53840,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1399" spans="1:14">
+    <row r="1399" spans="1:14" hidden="1">
       <c r="A1399" t="s">
         <v>577</v>
       </c>
@@ -53882,7 +53882,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1400" spans="1:14">
+    <row r="1400" spans="1:14" hidden="1">
       <c r="A1400" t="s">
         <v>577</v>
       </c>
@@ -53924,7 +53924,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1401" spans="1:14">
+    <row r="1401" spans="1:14" hidden="1">
       <c r="A1401" t="s">
         <v>577</v>
       </c>
@@ -53966,7 +53966,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1402" spans="1:14">
+    <row r="1402" spans="1:14" hidden="1">
       <c r="A1402" t="s">
         <v>577</v>
       </c>
@@ -54008,7 +54008,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1403" spans="1:14">
+    <row r="1403" spans="1:14" hidden="1">
       <c r="A1403" t="s">
         <v>577</v>
       </c>
@@ -54050,7 +54050,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1404" spans="1:14">
+    <row r="1404" spans="1:14" hidden="1">
       <c r="A1404" t="s">
         <v>579</v>
       </c>
@@ -54095,7 +54095,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1405" spans="1:14">
+    <row r="1405" spans="1:14" hidden="1">
       <c r="A1405" t="s">
         <v>579</v>
       </c>
@@ -54137,7 +54137,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1406" spans="1:14">
+    <row r="1406" spans="1:14" hidden="1">
       <c r="A1406" t="s">
         <v>579</v>
       </c>
@@ -54179,7 +54179,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1407" spans="1:14">
+    <row r="1407" spans="1:14" hidden="1">
       <c r="A1407" t="s">
         <v>579</v>
       </c>
@@ -54221,7 +54221,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1408" spans="1:14">
+    <row r="1408" spans="1:14" hidden="1">
       <c r="A1408" t="s">
         <v>579</v>
       </c>
@@ -54263,7 +54263,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1409" spans="1:14">
+    <row r="1409" spans="1:14" hidden="1">
       <c r="A1409" t="s">
         <v>579</v>
       </c>
@@ -54305,7 +54305,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1410" spans="1:14">
+    <row r="1410" spans="1:14" hidden="1">
       <c r="A1410" t="s">
         <v>579</v>
       </c>
@@ -54347,7 +54347,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1411" spans="1:14">
+    <row r="1411" spans="1:14" hidden="1">
       <c r="A1411" t="s">
         <v>579</v>
       </c>
@@ -54389,7 +54389,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1412" spans="1:14">
+    <row r="1412" spans="1:14" hidden="1">
       <c r="A1412" t="s">
         <v>579</v>
       </c>
@@ -54431,7 +54431,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1413" spans="1:14">
+    <row r="1413" spans="1:14" hidden="1">
       <c r="A1413" t="s">
         <v>579</v>
       </c>
@@ -54473,7 +54473,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1414" spans="1:14">
+    <row r="1414" spans="1:14" hidden="1">
       <c r="A1414" t="s">
         <v>579</v>
       </c>
@@ -54515,7 +54515,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1415" spans="1:14">
+    <row r="1415" spans="1:14" hidden="1">
       <c r="A1415" t="s">
         <v>579</v>
       </c>
@@ -54557,7 +54557,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1416" spans="1:14">
+    <row r="1416" spans="1:14" hidden="1">
       <c r="A1416" t="s">
         <v>579</v>
       </c>
@@ -54599,7 +54599,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1417" spans="1:14">
+    <row r="1417" spans="1:14" hidden="1">
       <c r="A1417" t="s">
         <v>579</v>
       </c>
@@ -54641,7 +54641,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1418" spans="1:14">
+    <row r="1418" spans="1:14" hidden="1">
       <c r="A1418" t="s">
         <v>579</v>
       </c>
@@ -54683,7 +54683,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1419" spans="1:14">
+    <row r="1419" spans="1:14" hidden="1">
       <c r="A1419" t="s">
         <v>579</v>
       </c>
@@ -54725,7 +54725,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1420" spans="1:14">
+    <row r="1420" spans="1:14" hidden="1">
       <c r="A1420" t="s">
         <v>579</v>
       </c>
@@ -54767,7 +54767,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1421" spans="1:14">
+    <row r="1421" spans="1:14" hidden="1">
       <c r="A1421" t="s">
         <v>579</v>
       </c>
@@ -54809,7 +54809,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1422" spans="1:14">
+    <row r="1422" spans="1:14" hidden="1">
       <c r="A1422" t="s">
         <v>579</v>
       </c>
@@ -54851,7 +54851,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1423" spans="1:14">
+    <row r="1423" spans="1:14" hidden="1">
       <c r="A1423" t="s">
         <v>580</v>
       </c>
@@ -54896,7 +54896,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1424" spans="1:14">
+    <row r="1424" spans="1:14" hidden="1">
       <c r="A1424" t="s">
         <v>580</v>
       </c>
@@ -54938,7 +54938,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1425" spans="1:14">
+    <row r="1425" spans="1:14" hidden="1">
       <c r="A1425" t="s">
         <v>580</v>
       </c>
@@ -54980,7 +54980,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1426" spans="1:14">
+    <row r="1426" spans="1:14" hidden="1">
       <c r="A1426" t="s">
         <v>580</v>
       </c>
@@ -55022,7 +55022,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1427" spans="1:14">
+    <row r="1427" spans="1:14" hidden="1">
       <c r="A1427" t="s">
         <v>580</v>
       </c>
@@ -55064,7 +55064,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1428" spans="1:14">
+    <row r="1428" spans="1:14" hidden="1">
       <c r="A1428" t="s">
         <v>580</v>
       </c>
@@ -55106,7 +55106,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1429" spans="1:14">
+    <row r="1429" spans="1:14" hidden="1">
       <c r="A1429" t="s">
         <v>580</v>
       </c>
@@ -55148,7 +55148,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1430" spans="1:14">
+    <row r="1430" spans="1:14" hidden="1">
       <c r="A1430" t="s">
         <v>580</v>
       </c>
@@ -55190,7 +55190,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1431" spans="1:14">
+    <row r="1431" spans="1:14" hidden="1">
       <c r="A1431" t="s">
         <v>580</v>
       </c>
@@ -55232,7 +55232,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1432" spans="1:14">
+    <row r="1432" spans="1:14" hidden="1">
       <c r="A1432" t="s">
         <v>580</v>
       </c>
@@ -55274,7 +55274,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1433" spans="1:14">
+    <row r="1433" spans="1:14" hidden="1">
       <c r="A1433" t="s">
         <v>582</v>
       </c>
@@ -55319,7 +55319,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1434" spans="1:14">
+    <row r="1434" spans="1:14" hidden="1">
       <c r="A1434" t="s">
         <v>582</v>
       </c>
@@ -55361,7 +55361,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1435" spans="1:14">
+    <row r="1435" spans="1:14" hidden="1">
       <c r="A1435" t="s">
         <v>582</v>
       </c>
@@ -55403,7 +55403,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1436" spans="1:14">
+    <row r="1436" spans="1:14" hidden="1">
       <c r="A1436" t="s">
         <v>582</v>
       </c>
@@ -55445,7 +55445,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1437" spans="1:14">
+    <row r="1437" spans="1:14" hidden="1">
       <c r="A1437" t="s">
         <v>582</v>
       </c>
@@ -55487,7 +55487,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1438" spans="1:14">
+    <row r="1438" spans="1:14" hidden="1">
       <c r="A1438" t="s">
         <v>582</v>
       </c>
@@ -55529,7 +55529,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1439" spans="1:14">
+    <row r="1439" spans="1:14" hidden="1">
       <c r="A1439" t="s">
         <v>582</v>
       </c>
@@ -55571,7 +55571,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1440" spans="1:14">
+    <row r="1440" spans="1:14" hidden="1">
       <c r="A1440" t="s">
         <v>582</v>
       </c>
@@ -55613,7 +55613,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1441" spans="1:14">
+    <row r="1441" spans="1:14" hidden="1">
       <c r="A1441" t="s">
         <v>582</v>
       </c>
@@ -55655,7 +55655,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1442" spans="1:14">
+    <row r="1442" spans="1:14" hidden="1">
       <c r="A1442" t="s">
         <v>582</v>
       </c>
@@ -60050,7 +60050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1574" spans="1:14">
+    <row r="1574" spans="1:14" hidden="1">
       <c r="A1574" t="s">
         <v>623</v>
       </c>
@@ -60095,7 +60095,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1575" spans="1:14">
+    <row r="1575" spans="1:14" hidden="1">
       <c r="A1575" t="s">
         <v>623</v>
       </c>
@@ -60137,7 +60137,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1576" spans="1:14">
+    <row r="1576" spans="1:14" hidden="1">
       <c r="A1576" t="s">
         <v>623</v>
       </c>
@@ -60179,7 +60179,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1577" spans="1:14">
+    <row r="1577" spans="1:14" hidden="1">
       <c r="A1577" t="s">
         <v>623</v>
       </c>
@@ -60221,7 +60221,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1578" spans="1:14">
+    <row r="1578" spans="1:14" hidden="1">
       <c r="A1578" t="s">
         <v>623</v>
       </c>
@@ -60263,7 +60263,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1579" spans="1:14">
+    <row r="1579" spans="1:14" hidden="1">
       <c r="A1579" t="s">
         <v>623</v>
       </c>
@@ -60305,7 +60305,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1580" spans="1:14">
+    <row r="1580" spans="1:14" hidden="1">
       <c r="A1580" t="s">
         <v>623</v>
       </c>
@@ -60347,7 +60347,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1581" spans="1:14">
+    <row r="1581" spans="1:14" hidden="1">
       <c r="A1581" t="s">
         <v>623</v>
       </c>
@@ -60389,7 +60389,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1582" spans="1:14">
+    <row r="1582" spans="1:14" hidden="1">
       <c r="A1582" t="s">
         <v>623</v>
       </c>
@@ -60431,7 +60431,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1583" spans="1:14">
+    <row r="1583" spans="1:14" hidden="1">
       <c r="A1583" t="s">
         <v>623</v>
       </c>
@@ -60473,7 +60473,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1584" spans="1:14">
+    <row r="1584" spans="1:14" hidden="1">
       <c r="A1584" t="s">
         <v>623</v>
       </c>
@@ -60515,7 +60515,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1585" spans="1:14">
+    <row r="1585" spans="1:14" hidden="1">
       <c r="A1585" t="s">
         <v>623</v>
       </c>
@@ -60557,7 +60557,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1586" spans="1:14">
+    <row r="1586" spans="1:14" hidden="1">
       <c r="A1586" t="s">
         <v>623</v>
       </c>
@@ -60599,7 +60599,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1587" spans="1:14">
+    <row r="1587" spans="1:14" hidden="1">
       <c r="A1587" t="s">
         <v>623</v>
       </c>
@@ -60641,7 +60641,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1588" spans="1:14">
+    <row r="1588" spans="1:14" hidden="1">
       <c r="A1588" t="s">
         <v>623</v>
       </c>
@@ -60683,7 +60683,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1589" spans="1:14">
+    <row r="1589" spans="1:14" hidden="1">
       <c r="A1589" t="s">
         <v>623</v>
       </c>
@@ -60725,7 +60725,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1590" spans="1:14">
+    <row r="1590" spans="1:14" hidden="1">
       <c r="A1590" t="s">
         <v>623</v>
       </c>
@@ -60767,7 +60767,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1591" spans="1:14">
+    <row r="1591" spans="1:14" hidden="1">
       <c r="A1591" t="s">
         <v>623</v>
       </c>
@@ -60809,7 +60809,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1592" spans="1:14">
+    <row r="1592" spans="1:14" hidden="1">
       <c r="A1592" t="s">
         <v>623</v>
       </c>
@@ -60851,7 +60851,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1593" spans="1:14">
+    <row r="1593" spans="1:14" hidden="1">
       <c r="A1593" t="s">
         <v>623</v>
       </c>
@@ -60893,7 +60893,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1594" spans="1:14">
+    <row r="1594" spans="1:14" hidden="1">
       <c r="A1594" t="s">
         <v>623</v>
       </c>
@@ -60935,7 +60935,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1595" spans="1:14">
+    <row r="1595" spans="1:14" hidden="1">
       <c r="A1595" t="s">
         <v>623</v>
       </c>
@@ -60977,7 +60977,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1596" spans="1:14">
+    <row r="1596" spans="1:14" hidden="1">
       <c r="A1596" t="s">
         <v>623</v>
       </c>
@@ -61019,7 +61019,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1597" spans="1:14">
+    <row r="1597" spans="1:14" hidden="1">
       <c r="A1597" t="s">
         <v>623</v>
       </c>
@@ -61061,7 +61061,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1598" spans="1:14">
+    <row r="1598" spans="1:14" hidden="1">
       <c r="A1598" t="s">
         <v>623</v>
       </c>
@@ -61103,7 +61103,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1599" spans="1:14">
+    <row r="1599" spans="1:14" hidden="1">
       <c r="A1599" t="s">
         <v>623</v>
       </c>
@@ -61145,7 +61145,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1600" spans="1:14">
+    <row r="1600" spans="1:14" hidden="1">
       <c r="A1600" t="s">
         <v>623</v>
       </c>
@@ -61187,7 +61187,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1601" spans="1:14">
+    <row r="1601" spans="1:14" hidden="1">
       <c r="A1601" t="s">
         <v>623</v>
       </c>
@@ -61229,7 +61229,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1602" spans="1:14">
+    <row r="1602" spans="1:14" hidden="1">
       <c r="A1602" t="s">
         <v>623</v>
       </c>
@@ -61271,7 +61271,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1603" spans="1:14">
+    <row r="1603" spans="1:14" hidden="1">
       <c r="A1603" t="s">
         <v>626</v>
       </c>
@@ -61316,7 +61316,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1604" spans="1:14">
+    <row r="1604" spans="1:14" hidden="1">
       <c r="A1604" t="s">
         <v>626</v>
       </c>
@@ -61358,7 +61358,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1605" spans="1:14">
+    <row r="1605" spans="1:14" hidden="1">
       <c r="A1605" t="s">
         <v>626</v>
       </c>
@@ -61400,7 +61400,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1606" spans="1:14">
+    <row r="1606" spans="1:14" hidden="1">
       <c r="A1606" t="s">
         <v>626</v>
       </c>
@@ -61442,7 +61442,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1607" spans="1:14">
+    <row r="1607" spans="1:14" hidden="1">
       <c r="A1607" t="s">
         <v>626</v>
       </c>
@@ -61484,7 +61484,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1608" spans="1:14">
+    <row r="1608" spans="1:14" hidden="1">
       <c r="A1608" t="s">
         <v>626</v>
       </c>
@@ -61526,7 +61526,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1609" spans="1:14">
+    <row r="1609" spans="1:14" hidden="1">
       <c r="A1609" t="s">
         <v>626</v>
       </c>
@@ -61568,7 +61568,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1610" spans="1:14">
+    <row r="1610" spans="1:14" hidden="1">
       <c r="A1610" t="s">
         <v>626</v>
       </c>
@@ -61610,7 +61610,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="1611" spans="1:14">
+    <row r="1611" spans="1:14" hidden="1">
       <c r="A1611" t="s">
         <v>626</v>
       </c>
@@ -64274,7 +64274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1691" spans="1:14">
+    <row r="1691" spans="1:14" hidden="1">
       <c r="A1691" t="s">
         <v>663</v>
       </c>
@@ -64319,7 +64319,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1692" spans="1:14">
+    <row r="1692" spans="1:14" hidden="1">
       <c r="A1692" t="s">
         <v>663</v>
       </c>
@@ -64361,7 +64361,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1693" spans="1:14">
+    <row r="1693" spans="1:14" hidden="1">
       <c r="A1693" t="s">
         <v>663</v>
       </c>
@@ -64403,7 +64403,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1694" spans="1:14">
+    <row r="1694" spans="1:14" hidden="1">
       <c r="A1694" t="s">
         <v>663</v>
       </c>
@@ -64445,7 +64445,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1695" spans="1:14">
+    <row r="1695" spans="1:14" hidden="1">
       <c r="A1695" t="s">
         <v>663</v>
       </c>
@@ -64487,7 +64487,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1696" spans="1:14">
+    <row r="1696" spans="1:14" hidden="1">
       <c r="A1696" t="s">
         <v>663</v>
       </c>
@@ -64529,7 +64529,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1697" spans="1:14">
+    <row r="1697" spans="1:14" hidden="1">
       <c r="A1697" t="s">
         <v>663</v>
       </c>
@@ -64571,7 +64571,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1698" spans="1:14">
+    <row r="1698" spans="1:14" hidden="1">
       <c r="A1698" t="s">
         <v>663</v>
       </c>
@@ -64613,7 +64613,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1699" spans="1:14">
+    <row r="1699" spans="1:14" hidden="1">
       <c r="A1699" t="s">
         <v>663</v>
       </c>
@@ -64655,7 +64655,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1700" spans="1:14">
+    <row r="1700" spans="1:14" hidden="1">
       <c r="A1700" t="s">
         <v>663</v>
       </c>
@@ -64697,7 +64697,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1701" spans="1:14">
+    <row r="1701" spans="1:14" hidden="1">
       <c r="A1701" t="s">
         <v>663</v>
       </c>
@@ -64739,7 +64739,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1702" spans="1:14">
+    <row r="1702" spans="1:14" hidden="1">
       <c r="A1702" t="s">
         <v>663</v>
       </c>
@@ -64781,7 +64781,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1703" spans="1:14">
+    <row r="1703" spans="1:14" hidden="1">
       <c r="A1703" t="s">
         <v>663</v>
       </c>
@@ -64823,7 +64823,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1704" spans="1:14">
+    <row r="1704" spans="1:14" hidden="1">
       <c r="A1704" t="s">
         <v>663</v>
       </c>
@@ -64865,7 +64865,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1705" spans="1:14">
+    <row r="1705" spans="1:14" hidden="1">
       <c r="A1705" t="s">
         <v>663</v>
       </c>
@@ -64907,7 +64907,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1706" spans="1:14">
+    <row r="1706" spans="1:14" hidden="1">
       <c r="A1706" t="s">
         <v>663</v>
       </c>
@@ -64949,7 +64949,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1707" spans="1:14" ht="15.75" thickBot="1">
+    <row r="1707" spans="1:14" ht="15.75" hidden="1" thickBot="1">
       <c r="A1707" s="5" t="s">
         <v>663</v>
       </c>
@@ -64992,7 +64992,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="1708" spans="1:14">
+    <row r="1708" spans="1:14" hidden="1">
       <c r="K1708" s="3">
         <f>AVERAGE(K3:K1707)</f>
         <v>0.39824046920821116</v>
@@ -65004,6 +65004,11 @@
       <filters blank="1">
         <filter val="System"/>
         <filter val="TMS"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <filters>
+        <filter val="0.00%"/>
       </filters>
     </filterColumn>
   </autoFilter>
